--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.30114960843805</v>
+        <v>6.873936811371184</v>
       </c>
       <c r="D2" t="n">
-        <v>75.3722953477822</v>
+        <v>12.24799799401461</v>
       </c>
       <c r="E2" t="n">
-        <v>7.985610445399888</v>
+        <v>1.297661697377482</v>
       </c>
       <c r="F2" t="n">
-        <v>24.88626587642081</v>
+        <v>4.044018204918381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.0822094144321</v>
+        <v>3.425859029845217</v>
       </c>
       <c r="D3" t="n">
-        <v>47.2619767301839</v>
+        <v>7.680071218654883</v>
       </c>
       <c r="E3" t="n">
-        <v>7.985610445399888</v>
+        <v>1.297661697377482</v>
       </c>
       <c r="F3" t="n">
-        <v>24.88626587642081</v>
+        <v>4.044018204918381</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.71275957960837</v>
+        <v>6.615823431686361</v>
       </c>
       <c r="D4" t="n">
-        <v>55.96275976648374</v>
+        <v>9.093948462053609</v>
       </c>
       <c r="E4" t="n">
-        <v>7.985610445399888</v>
+        <v>1.297661697377482</v>
       </c>
       <c r="F4" t="n">
-        <v>24.88626587642081</v>
+        <v>4.044018204918381</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.35364034756759</v>
+        <v>5.419966556479734</v>
       </c>
       <c r="D5" t="n">
-        <v>10.14615417014962</v>
+        <v>1.648750052649313</v>
       </c>
       <c r="E5" t="n">
-        <v>7.985610445399888</v>
+        <v>1.297661697377482</v>
       </c>
       <c r="F5" t="n">
-        <v>24.88626587642081</v>
+        <v>4.044018204918381</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.4597228110457</v>
+        <v>4.462204956794927</v>
       </c>
       <c r="D6" t="n">
-        <v>14.52893586282152</v>
+        <v>2.360952077708497</v>
       </c>
       <c r="E6" t="n">
-        <v>7.985610445399888</v>
+        <v>1.297661697377482</v>
       </c>
       <c r="F6" t="n">
-        <v>24.88626587642081</v>
+        <v>4.044018204918381</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
